--- a/光伏配储项目/电价数据/2026/都杨站.xlsx
+++ b/光伏配储项目/电价数据/2026/都杨站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51034</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7430099999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57097</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5787100000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45439</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44046</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09484999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10325</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08940000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09540000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.12811</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.12415</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08992</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.10876</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01539</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15205</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21646</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25536</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21133</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10002</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.005719999999999999</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14179</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18737</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55672</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48986</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.9590700000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59251</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44211</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44526</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56764</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44828</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60093</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79787</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6362100000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.61568</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73202</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.87464</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66184</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.62418</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.68264</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6171599999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6139600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63462</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6047100000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46801</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48882</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42594</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68914</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77356</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7814099999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.24501</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8474700000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5276000000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51908</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50727</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48963</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59693</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69459</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50614</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15847</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.48687</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.79138</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9642999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.80604</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.49266</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10944</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47329</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.47833</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.55569</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.68349</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5292100000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68652</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76119</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.51423</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8247000000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.9639500000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.61734</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5361699999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5294500000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45408</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19879</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46652</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14801</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.42499</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.46507</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.5942200000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51609</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6003999999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5448500000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58887</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45456</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4723</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34251</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46079</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12629</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20293</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16356</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50062</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.0707</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06272</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.13987</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.16391</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.18143</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50918</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05471</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12304</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21177</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22391</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24246</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.21048</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26934</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14067</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.57905</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29736</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26031</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05321</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05317</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04638</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04753</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04735</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04244</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04259</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04171</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04625</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04435</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04661999999999999</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.0481</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04618999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05185</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05547</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05472</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11251</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35101</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6794600000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44633</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03967</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10414</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00145</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04541</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.0454</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04507</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04521</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04333</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04401</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04283</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04453</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04761</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20024</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14305</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3358</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31815</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17262</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15887</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17122</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14794</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15967</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15885</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23656</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21427</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27095</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45445</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15662</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49796</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9167799999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.87081</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30053</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8953099999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6329600000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19477</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8725499999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5473600000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33871</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03832</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79765</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53052</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7796799999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78286</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8776</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87737</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49941</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45712</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2151</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8791599999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62988</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5403600000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58689</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60222</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6662400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46776</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87703</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63224</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86794</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.84999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86172</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44086</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45259</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35346</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92703</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46798</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38779</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16535</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19933</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20102</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27753</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25563</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59712</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89027</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.29962</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.11029</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68625</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7722100000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6362000000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57064</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49296</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42935</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49194</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.57356</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5794199999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26216</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25667</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7439199999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42239</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32421</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.21733</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24159</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15576</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.16708</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.03617</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.10785</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15055</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15151</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15047</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15233</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1581</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15692</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.16799</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.12242</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16054</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15048</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15519</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34899</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5306900000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46201</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19806</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24839</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24047</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35889</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.007809999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22207</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5392100000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28727</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34959</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.69764</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76742</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45532</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35194</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41987</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21821</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14981</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5944299999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6698</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.70008</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74152</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.53534</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8967000000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48315</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48356</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43038</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36004</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.56626</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.50958</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44482</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45756</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49268</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.60929</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46724</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64152</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15689</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48631</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50614</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5471200000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.62027</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.80049</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.81865</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.86554</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6979500000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80569</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.6069500000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.56188</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.95138</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.8720800000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6327999999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.71614</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47299</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49894</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5693400000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42886</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45866</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4729</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18286</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11039</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18063</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36544</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27251</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23054</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25306</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13978</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04326</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25128</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16935</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18107</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27217</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23276</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35031</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24422</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16766</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20658</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21404</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01793</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00044</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10775</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01671</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02026</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04265</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04046</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02656</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03024</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.13337</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00284</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03387</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04323</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19721</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23635</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27971</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26622</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13944</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5697000000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.16353</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25854</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23906</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22245</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24886</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27074</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.16089</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6369400000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.63312</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.65591</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57509</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.16235</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09253</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23785</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17763</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.12137</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12915</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.08375</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22838</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.11137</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.03652</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.04665999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.10146</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17599</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.12052</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.12664</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.14773</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01744</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.11107</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.11194</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14395</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25483</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3236</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.03244</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.56904</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.47708</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14026</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37255</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.64813</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.61695</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41638</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46047</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47483</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.47835</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41791</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.57821</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37753</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43049</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.52128</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6071299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.60636</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.58261</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52259</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.57309</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.52844</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.57172</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.49317</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.09918</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.92743</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6247699999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6159600000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38167</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.22995</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17294</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05988</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.15261</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02856</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19663</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16303</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-2e-05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06543</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.15044</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07271</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05451</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16949</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14198</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16352</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28217</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.45287</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.5885</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38105</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.99009</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36464</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.26226</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26229</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11336</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04255</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16936</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04102</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01614</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16417</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26694</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23977</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.15962</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5789500000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.65687</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37508</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6239400000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44599</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23222</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14502</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20921</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23537</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11504</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15202</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.00511</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04643</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04494</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07948999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02912</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06397</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09779</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17241</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19685</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12156</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23078</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04775</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14796</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11781</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23758</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18797</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24198</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20593</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27819</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5182899999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3826</v>
       </c>
     </row>
   </sheetData>
